--- a/uloha4/uloha4.xlsx
+++ b/uloha4/uloha4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF9C825-53C2-400D-9F82-38DBAAF7BAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA607B9-9DDA-47C1-A4B5-705623BA0BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5221C9AC-7A57-4770-B266-F8BD59E37F47}"/>
   </bookViews>
@@ -806,12 +806,12 @@
         <v>1475.6</v>
       </c>
       <c r="I19">
-        <f>H19-$B$46</f>
-        <v>1448.6</v>
+        <f>H19</f>
+        <v>1475.6</v>
       </c>
       <c r="J19">
         <f>I19/F19*3.14159265/4*G28^2*10</f>
-        <v>21.273864239710765</v>
+        <v>21.670381107356896</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -912,12 +912,12 @@
         <v>6284</v>
       </c>
       <c r="D27">
-        <f>C27-$B$46</f>
-        <v>6257</v>
+        <f>C27</f>
+        <v>6284</v>
       </c>
       <c r="E27">
         <f>D27/A19*3.14159265/4*B28^2*10</f>
-        <v>137.3583770857116</v>
+        <v>137.95110142346363</v>
       </c>
       <c r="G27">
         <v>0.41</v>
@@ -926,12 +926,12 @@
         <v>1482</v>
       </c>
       <c r="I27">
-        <f>H27-$B$46</f>
-        <v>1455</v>
+        <f>H27</f>
+        <v>1482</v>
       </c>
       <c r="J27">
         <f>I27/F19*3.14159265/4*G28^2*10</f>
-        <v>21.367853423152813</v>
+        <v>21.764370290798944</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -1021,12 +1021,12 @@
         <v>220.82</v>
       </c>
       <c r="D34">
-        <f>C34-$B$46</f>
-        <v>193.82</v>
+        <f>C34</f>
+        <v>220.82</v>
       </c>
       <c r="E34">
         <f>D34/A34*3.14159265/4*B43^2*10</f>
-        <v>6.0350023094811984</v>
+        <v>6.8757053450605641</v>
       </c>
       <c r="F34">
         <v>89.8</v>
@@ -1038,12 +1038,12 @@
         <v>1179.27</v>
       </c>
       <c r="I34">
-        <f>H34-$B$46</f>
-        <v>1152.27</v>
+        <f>H34</f>
+        <v>1179.27</v>
       </c>
       <c r="J34">
         <f>I34/F34*3.14159265/4*G43^2*10</f>
-        <v>101.58631920727811</v>
+        <v>103.96669066413848</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -1144,12 +1144,12 @@
         <v>221.4</v>
       </c>
       <c r="D42">
-        <f>C42-$B$46</f>
-        <v>194.4</v>
+        <f>C42</f>
+        <v>221.4</v>
       </c>
       <c r="E42">
         <f>D42/A34*3.14159265/4*B43^2*10</f>
-        <v>6.0530618561714222</v>
+        <v>6.8937648917507861</v>
       </c>
       <c r="G42">
         <v>1.02</v>
@@ -1158,12 +1158,12 @@
         <v>1179</v>
       </c>
       <c r="I42">
-        <f>H42-$B$46</f>
-        <v>1152</v>
+        <f>H42</f>
+        <v>1179</v>
       </c>
       <c r="J42">
         <f>I42/F34*3.14159265/4*G43^2*10</f>
-        <v>101.56251549270951</v>
+        <v>103.9428869495699</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">

--- a/uloha4/uloha4.xlsx
+++ b/uloha4/uloha4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA607B9-9DDA-47C1-A4B5-705623BA0BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F3E035-C368-4C73-B313-A0820CFDAB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5221C9AC-7A57-4770-B266-F8BD59E37F47}"/>
   </bookViews>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="24">
   <si>
     <t>D (mm)</t>
   </si>
@@ -96,6 +118,18 @@
   </si>
   <si>
     <t>+-0,4</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>t</t>
   </si>
 </sst>
 </file>
@@ -469,21 +503,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FD22E3-B841-455A-ACB8-0F57C9B9888A}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:Z46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.77734375" customWidth="1"/>
     <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" customWidth="1"/>
     <col min="4" max="4" width="8.33203125" customWidth="1"/>
     <col min="6" max="6" width="8.77734375" customWidth="1"/>
     <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" customWidth="1"/>
     <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" customWidth="1"/>
+    <col min="17" max="17" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -500,7 +536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -526,7 +562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.1</v>
       </c>
@@ -546,7 +582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>89.9</v>
       </c>
@@ -581,24 +617,101 @@
         <f>I4/F4*3.14159265/4*G13^2*10</f>
         <v>1.6705882527680584</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N4">
+        <v>136.93</v>
+      </c>
+      <c r="O4">
+        <v>10.59</v>
+      </c>
+      <c r="P4">
+        <v>6287.32</v>
+      </c>
+      <c r="Q4">
+        <v>1475.6</v>
+      </c>
+      <c r="R4">
+        <v>220.82</v>
+      </c>
+      <c r="S4">
+        <v>1179.27</v>
+      </c>
+      <c r="U4">
+        <v>89.9</v>
+      </c>
+      <c r="V4">
+        <v>90.2</v>
+      </c>
+      <c r="W4">
+        <v>89.8</v>
+      </c>
+      <c r="X4">
+        <v>89.9</v>
+      </c>
+      <c r="Y4">
+        <v>89.9</v>
+      </c>
+      <c r="Z4">
+        <v>89.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>0.69</v>
       </c>
       <c r="G5">
         <v>1.35</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N5">
+        <v>0.1</v>
+      </c>
+      <c r="O5">
+        <v>0.09</v>
+      </c>
+      <c r="P5">
+        <v>0.5</v>
+      </c>
+      <c r="Q5">
+        <v>0.2</v>
+      </c>
+      <c r="R5">
+        <v>0.1</v>
+      </c>
+      <c r="S5">
+        <v>0.16</v>
+      </c>
+      <c r="U5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>0.69</v>
       </c>
       <c r="G6">
         <v>1.34</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N6">
+        <v>136.9</v>
+      </c>
+      <c r="O6">
+        <f>O4</f>
+        <v>10.59</v>
+      </c>
+      <c r="P6">
+        <v>6287.3</v>
+      </c>
+      <c r="Q6">
+        <v>1475.6</v>
+      </c>
+      <c r="R6">
+        <v>220.8</v>
+      </c>
+      <c r="S6">
+        <f>S4</f>
+        <v>1179.27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>0.69</v>
       </c>
@@ -612,7 +725,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>0.68</v>
       </c>
@@ -642,7 +755,7 @@
         <v>1.7825918089026493</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>0.69</v>
       </c>
@@ -650,7 +763,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>0.69</v>
       </c>
@@ -658,7 +771,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>0.68</v>
       </c>
@@ -671,8 +784,26 @@
       <c r="H11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O11">
+        <v>0.69</v>
+      </c>
+      <c r="P11">
+        <v>1.34</v>
+      </c>
+      <c r="Q11">
+        <v>0.5</v>
+      </c>
+      <c r="R11">
+        <v>0.41</v>
+      </c>
+      <c r="S11">
+        <v>0.59</v>
+      </c>
+      <c r="T11">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>0.69</v>
       </c>
@@ -701,8 +832,26 @@
         <f>I12/F4*3.14159265/4*G13^2*10</f>
         <v>1.7194912138972465</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O12">
+        <v>0.68</v>
+      </c>
+      <c r="P12">
+        <v>1.35</v>
+      </c>
+      <c r="Q12">
+        <v>0.5</v>
+      </c>
+      <c r="R12">
+        <v>0.41</v>
+      </c>
+      <c r="S12">
+        <v>0.6</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -717,8 +866,66 @@
         <f>AVERAGE(G3:G12)</f>
         <v>1.3459999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O13">
+        <v>0.69</v>
+      </c>
+      <c r="P13">
+        <v>1.35</v>
+      </c>
+      <c r="Q13">
+        <v>0.5</v>
+      </c>
+      <c r="R13">
+        <v>0.41</v>
+      </c>
+      <c r="S13">
+        <v>0.6</v>
+      </c>
+      <c r="T13">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="O14">
+        <v>0.69</v>
+      </c>
+      <c r="P14">
+        <v>1.34</v>
+      </c>
+      <c r="Q14">
+        <v>0.49</v>
+      </c>
+      <c r="R14">
+        <v>0.41</v>
+      </c>
+      <c r="S14">
+        <v>0.6</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="O15">
+        <v>0.69</v>
+      </c>
+      <c r="P15">
+        <v>1.35</v>
+      </c>
+      <c r="Q15">
+        <v>0.5</v>
+      </c>
+      <c r="R15">
+        <v>0.41</v>
+      </c>
+      <c r="S15">
+        <v>0.59</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -731,8 +938,26 @@
       <c r="G16">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O16">
+        <v>0.68</v>
+      </c>
+      <c r="P16">
+        <v>1.35</v>
+      </c>
+      <c r="Q16">
+        <v>0.5</v>
+      </c>
+      <c r="R16">
+        <v>0.41</v>
+      </c>
+      <c r="S16">
+        <v>0.61</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -757,8 +982,26 @@
       <c r="J17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O17">
+        <v>0.69</v>
+      </c>
+      <c r="P17">
+        <v>1.35</v>
+      </c>
+      <c r="Q17">
+        <v>0.51</v>
+      </c>
+      <c r="R17">
+        <v>0.41</v>
+      </c>
+      <c r="S17">
+        <v>0.59</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.1</v>
       </c>
@@ -777,8 +1020,26 @@
       <c r="H18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O18">
+        <v>0.69</v>
+      </c>
+      <c r="P18">
+        <v>1.35</v>
+      </c>
+      <c r="Q18">
+        <v>0.51</v>
+      </c>
+      <c r="R18">
+        <v>0.41</v>
+      </c>
+      <c r="S18">
+        <v>0.6</v>
+      </c>
+      <c r="T18">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>89.8</v>
       </c>
@@ -813,16 +1074,52 @@
         <f>I19/F19*3.14159265/4*G28^2*10</f>
         <v>21.670381107356896</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O19">
+        <v>0.68</v>
+      </c>
+      <c r="P19">
+        <v>1.34</v>
+      </c>
+      <c r="Q19">
+        <v>0.5</v>
+      </c>
+      <c r="R19">
+        <v>0.41</v>
+      </c>
+      <c r="S19">
+        <v>0.6</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>0.5</v>
       </c>
       <c r="G20">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O20">
+        <v>0.69</v>
+      </c>
+      <c r="P20">
+        <v>1.34</v>
+      </c>
+      <c r="Q20">
+        <v>0.5</v>
+      </c>
+      <c r="R20">
+        <v>0.41</v>
+      </c>
+      <c r="S20">
+        <v>0.59</v>
+      </c>
+      <c r="T20">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>0.49</v>
       </c>
@@ -830,7 +1127,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>0.5</v>
       </c>
@@ -843,8 +1140,31 @@
       <c r="H22" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O22">
+        <v>169.1</v>
+      </c>
+      <c r="P22">
+        <f>H8</f>
+        <v>38.299999999999997</v>
+      </c>
+      <c r="Q22">
+        <f>C23</f>
+        <v>6311</v>
+      </c>
+      <c r="R22">
+        <f>H23</f>
+        <v>1508</v>
+      </c>
+      <c r="S22">
+        <f>C38</f>
+        <v>250</v>
+      </c>
+      <c r="T22">
+        <f>H38</f>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>0.5</v>
       </c>
@@ -873,8 +1193,32 @@
         <f>I23/F19*3.14159265/4*G28^2*10</f>
         <v>21.749684480886128</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O23">
+        <f>D8</f>
+        <v>142.1</v>
+      </c>
+      <c r="P23">
+        <f>I8</f>
+        <v>11.299999999999997</v>
+      </c>
+      <c r="Q23">
+        <f>D23</f>
+        <v>6284</v>
+      </c>
+      <c r="R23">
+        <f>I23</f>
+        <v>1481</v>
+      </c>
+      <c r="S23">
+        <f>D38</f>
+        <v>223</v>
+      </c>
+      <c r="T23">
+        <f>I38</f>
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>0.51</v>
       </c>
@@ -882,7 +1226,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>0.51</v>
       </c>
@@ -890,7 +1234,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>0.5</v>
       </c>
@@ -903,8 +1247,26 @@
       <c r="H26" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="O26">
+        <v>137.6</v>
+      </c>
+      <c r="P26">
+        <v>10.9</v>
+      </c>
+      <c r="Q26">
+        <v>6284</v>
+      </c>
+      <c r="R26">
+        <v>1482</v>
+      </c>
+      <c r="S26">
+        <v>221.4</v>
+      </c>
+      <c r="T26">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>0.5</v>
       </c>
@@ -934,7 +1296,7 @@
         <v>21.764370290798944</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -950,7 +1312,52 @@
         <v>0.41000000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N29" t="s">
+        <v>20</v>
+      </c>
+      <c r="P29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>22</v>
+      </c>
+      <c r="T29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N30" cm="1">
+        <f t="array" ref="N30:N35">_xlfn.TOCOL(U4:Z4)</f>
+        <v>89.9</v>
+      </c>
+      <c r="O30">
+        <v>0.1</v>
+      </c>
+      <c r="P30" cm="1">
+        <f t="array" ref="P30:P35">_xlfn.TOCOL(N6:S6)</f>
+        <v>136.9</v>
+      </c>
+      <c r="Q30" cm="1">
+        <f t="array" ref="Q30:Q35">_xlfn.TOCOL(N5:S5)</f>
+        <v>0.1</v>
+      </c>
+      <c r="R30" cm="1">
+        <f t="array" ref="R30:R35">_xlfn.TOCOL(O23:T23)</f>
+        <v>142.1</v>
+      </c>
+      <c r="S30">
+        <v>0.1</v>
+      </c>
+      <c r="T30" cm="1">
+        <f t="array" ref="T30:T35">_xlfn.TOCOL(O26:T26)</f>
+        <v>137.6</v>
+      </c>
+      <c r="U30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -963,8 +1370,32 @@
       <c r="G31">
         <v>110</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N31">
+        <v>90.2</v>
+      </c>
+      <c r="O31">
+        <v>0.1</v>
+      </c>
+      <c r="P31">
+        <v>10.59</v>
+      </c>
+      <c r="Q31">
+        <v>0.09</v>
+      </c>
+      <c r="R31">
+        <v>11.299999999999997</v>
+      </c>
+      <c r="S31">
+        <v>0.1</v>
+      </c>
+      <c r="T31">
+        <v>10.9</v>
+      </c>
+      <c r="U31">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1</v>
       </c>
@@ -989,8 +1420,32 @@
       <c r="J32" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N32">
+        <v>89.8</v>
+      </c>
+      <c r="O32">
+        <v>0.1</v>
+      </c>
+      <c r="P32">
+        <v>6287.3</v>
+      </c>
+      <c r="Q32">
+        <v>0.5</v>
+      </c>
+      <c r="R32">
+        <v>6284</v>
+      </c>
+      <c r="S32">
+        <v>1</v>
+      </c>
+      <c r="T32">
+        <v>6284</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.1</v>
       </c>
@@ -1009,8 +1464,32 @@
       <c r="H33" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N33">
+        <v>89.9</v>
+      </c>
+      <c r="O33">
+        <v>0.1</v>
+      </c>
+      <c r="P33">
+        <v>1475.6</v>
+      </c>
+      <c r="Q33">
+        <v>0.2</v>
+      </c>
+      <c r="R33">
+        <v>1481</v>
+      </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>1482</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>89.9</v>
       </c>
@@ -1045,16 +1524,64 @@
         <f>I34/F34*3.14159265/4*G43^2*10</f>
         <v>103.96669066413848</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N34">
+        <v>89.9</v>
+      </c>
+      <c r="O34">
+        <v>0.1</v>
+      </c>
+      <c r="P34">
+        <v>220.8</v>
+      </c>
+      <c r="Q34">
+        <v>0.1</v>
+      </c>
+      <c r="R34">
+        <v>223</v>
+      </c>
+      <c r="S34">
+        <v>1</v>
+      </c>
+      <c r="T34">
+        <v>221.4</v>
+      </c>
+      <c r="U34">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>0.6</v>
       </c>
       <c r="G35">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N35">
+        <v>89.8</v>
+      </c>
+      <c r="O35">
+        <v>0.1</v>
+      </c>
+      <c r="P35">
+        <v>1179.27</v>
+      </c>
+      <c r="Q35">
+        <v>0.16</v>
+      </c>
+      <c r="R35">
+        <v>1181</v>
+      </c>
+      <c r="S35">
+        <v>1</v>
+      </c>
+      <c r="T35">
+        <v>1179</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>0.6</v>
       </c>
@@ -1062,7 +1589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>0.59</v>
       </c>
@@ -1076,7 +1603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>0.61</v>
       </c>
@@ -1106,7 +1633,7 @@
         <v>104.11921076118917</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>0.59</v>
       </c>
@@ -1114,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>0.6</v>
       </c>
@@ -1122,7 +1649,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>0.6</v>
       </c>
@@ -1136,7 +1663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>0.59</v>
       </c>
@@ -1166,7 +1693,7 @@
         <v>103.9428869495699</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -1182,7 +1709,7 @@
         <v>1.004</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>15</v>
       </c>
@@ -1190,7 +1717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>27</v>
       </c>
